--- a/data/grades/datascience_emlyon.xlsx
+++ b/data/grades/datascience_emlyon.xlsx
@@ -1,43 +1,101 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/guillaumemetzler/Documents/GuillaumeMetzler.github.io/data/grades/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763F06E2-BA85-A546-94AC-CD867505B5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1680" yWindow="1080" windowWidth="27040" windowHeight="15860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="notes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="notes" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>annee</t>
+  </si>
+  <si>
+    <t>Moyenne</t>
+  </si>
+  <si>
+    <t>Examen</t>
+  </si>
+  <si>
+    <t>Projet</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -45,88 +103,129 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="22">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -414,28 +513,867 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D72"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col min="1" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>annee</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
+    <row r="1" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="7">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="7">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="7">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="7">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="7">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>2024</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="7">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="8">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="13">
+        <v>2025</v>
+      </c>
+      <c r="B40" s="14">
+        <v>14.5</v>
+      </c>
+      <c r="C40" s="14">
+        <v>14.5</v>
+      </c>
+      <c r="D40" s="15">
+        <v>14.5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B41" s="16">
+        <v>11.5</v>
+      </c>
+      <c r="C41" s="16">
+        <v>12</v>
+      </c>
+      <c r="D41" s="17">
+        <v>11.83</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B42" s="16">
+        <v>7</v>
+      </c>
+      <c r="C42" s="16">
+        <v>19</v>
+      </c>
+      <c r="D42" s="17">
+        <v>14.92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B43" s="16">
+        <v>6.5</v>
+      </c>
+      <c r="C43" s="16">
+        <v>12</v>
+      </c>
+      <c r="D43" s="17">
+        <v>10.130000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B44" s="16">
+        <v>6.5</v>
+      </c>
+      <c r="C44" s="16">
+        <v>12</v>
+      </c>
+      <c r="D44" s="17">
+        <v>10.130000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B45" s="16">
+        <v>8.5</v>
+      </c>
+      <c r="C45" s="16">
+        <v>17</v>
+      </c>
+      <c r="D45" s="17">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B46" s="16">
+        <v>5</v>
+      </c>
+      <c r="C46" s="16">
+        <v>16</v>
+      </c>
+      <c r="D46" s="17">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B47" s="16">
+        <v>5</v>
+      </c>
+      <c r="C47" s="16">
+        <v>16</v>
+      </c>
+      <c r="D47" s="17">
+        <v>12.26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A48" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B48" s="16">
+        <v>6.5</v>
+      </c>
+      <c r="C48" s="16">
+        <v>15</v>
+      </c>
+      <c r="D48" s="17">
+        <v>12.11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A49" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B49" s="16">
+        <v>14</v>
+      </c>
+      <c r="C49" s="16">
+        <v>14</v>
+      </c>
+      <c r="D49" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A50" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B50" s="16">
+        <v>8</v>
+      </c>
+      <c r="C50" s="16">
+        <v>5</v>
+      </c>
+      <c r="D50" s="17">
+        <v>6.02</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A51" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B51" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="C51" s="16">
+        <v>12</v>
+      </c>
+      <c r="D51" s="17">
+        <v>10.47</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A52" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B52" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="C52" s="16">
+        <v>5</v>
+      </c>
+      <c r="D52" s="17">
+        <v>5.17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A53" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B53" s="16">
+        <v>6</v>
+      </c>
+      <c r="C53" s="16">
+        <v>15</v>
+      </c>
+      <c r="D53" s="17">
+        <v>11.94</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A54" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B54" s="16">
+        <v>11.5</v>
+      </c>
+      <c r="C54" s="16">
+        <v>15</v>
+      </c>
+      <c r="D54" s="17">
+        <v>13.81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A55" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B55" s="16">
+        <v>10.5</v>
+      </c>
+      <c r="C55" s="16">
+        <v>15</v>
+      </c>
+      <c r="D55" s="17">
+        <v>13.47</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A56" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B56" s="16">
+        <v>4</v>
+      </c>
+      <c r="C56" s="16">
+        <v>15</v>
+      </c>
+      <c r="D56" s="17">
+        <v>11.26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A57" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B57" s="16">
+        <v>19</v>
+      </c>
+      <c r="C57" s="16">
+        <v>19</v>
+      </c>
+      <c r="D57" s="17">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A58" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B58" s="16">
+        <v>5.5</v>
+      </c>
+      <c r="C58" s="16">
+        <v>14.5</v>
+      </c>
+      <c r="D58" s="17">
+        <v>11.44</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A59" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B59" s="16">
+        <v>3</v>
+      </c>
+      <c r="C59" s="18">
+        <v>0</v>
+      </c>
+      <c r="D59" s="17">
+        <v>1.02</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A60" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B60" s="16">
+        <v>4</v>
+      </c>
+      <c r="C60" s="16">
+        <v>6</v>
+      </c>
+      <c r="D60" s="17">
+        <v>5.32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A61" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B61" s="16">
+        <v>4</v>
+      </c>
+      <c r="C61" s="16">
+        <v>16</v>
+      </c>
+      <c r="D61" s="17">
+        <v>11.92</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A62" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B62" s="16">
+        <v>13</v>
+      </c>
+      <c r="C62" s="16">
+        <v>17</v>
+      </c>
+      <c r="D62" s="17">
+        <v>15.64</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A63" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B63" s="16">
+        <v>9</v>
+      </c>
+      <c r="C63" s="16">
+        <v>16</v>
+      </c>
+      <c r="D63" s="17">
+        <v>13.62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A64" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B64" s="16">
+        <v>7</v>
+      </c>
+      <c r="C64" s="16">
+        <v>15</v>
+      </c>
+      <c r="D64" s="17">
+        <v>12.28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A65" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B65" s="16">
+        <v>3.5</v>
+      </c>
+      <c r="C65" s="16">
+        <v>14</v>
+      </c>
+      <c r="D65" s="17">
+        <v>10.43</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A66" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B66" s="16">
+        <v>8.5</v>
+      </c>
+      <c r="C66" s="16">
+        <v>12</v>
+      </c>
+      <c r="D66" s="17">
+        <v>10.81</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A67" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B67" s="16">
+        <v>8</v>
+      </c>
+      <c r="C67" s="16">
+        <v>14</v>
+      </c>
+      <c r="D67" s="17">
+        <v>11.96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A68" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B68" s="16">
+        <v>15.5</v>
+      </c>
+      <c r="C68" s="16">
+        <v>16</v>
+      </c>
+      <c r="D68" s="17">
+        <v>15.83</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A69" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B69" s="16">
+        <v>6.5</v>
+      </c>
+      <c r="C69" s="16">
+        <v>16</v>
+      </c>
+      <c r="D69" s="17">
+        <v>12.77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A70" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B70" s="16">
+        <v>12.5</v>
+      </c>
+      <c r="C70" s="16">
+        <v>15</v>
+      </c>
+      <c r="D70" s="17">
+        <v>14.15</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A71" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B71" s="16">
+        <v>7.5</v>
+      </c>
+      <c r="C71" s="18">
+        <v>0</v>
+      </c>
+      <c r="D71" s="17">
+        <v>2.5499999999999998</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="19">
+        <v>2025</v>
+      </c>
+      <c r="B72" s="20">
+        <v>11.5</v>
+      </c>
+      <c r="C72" s="20">
+        <v>15</v>
+      </c>
+      <c r="D72" s="21">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
